--- a/verification/cases/roundtrip/styles/init.xlsx
+++ b/verification/cases/roundtrip/styles/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8069737E-C593-4DC6-845E-52F2C4301FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="570" windowWidth="14055" windowHeight="7110"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,11 +74,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00;[Red][$$-409]\-#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -201,22 +207,30 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Default" xfId="1"/>
-    <cellStyle name="Heading" xfId="4"/>
-    <cellStyle name="Heading1" xfId="5"/>
+    <cellStyle name="Default" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Heading" xfId="4" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Heading1" xfId="5" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Result" xfId="2"/>
-    <cellStyle name="Result2" xfId="3"/>
+    <cellStyle name="Result" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Result2" xfId="3" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -254,7 +268,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -288,6 +302,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -322,9 +337,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,15 +513,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.1" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="7" customWidth="1"/>
-    <col min="2" max="256" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="7" customWidth="1"/>
+    <col min="2" max="256" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +529,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -521,7 +537,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -529,7 +545,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1">
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -537,7 +553,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1">
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -545,7 +561,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" customHeight="1">
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -553,7 +569,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" customHeight="1">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -561,7 +577,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" customHeight="1">
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -569,7 +585,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -577,7 +593,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" customHeight="1">
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
@@ -585,7 +601,7 @@
         <v>4995</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.1" customHeight="1">
+    <row r="11" spans="1:2" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>10</v>
       </c>
@@ -597,11 +613,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IV1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="256" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="256" width="8.44140625" style="8" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -610,11 +626,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IV1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="256" width="8.42578125" style="8" customWidth="1"/>
+    <col min="1" max="256" width="8.44140625" style="8" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.31496062992125984" footer="0.31496062992125984"/>
